--- a/results/by_outcome/full_results_education_PGI_sons.xlsx
+++ b/results/by_outcome/full_results_education_PGI_sons.xlsx
@@ -468,32 +468,32 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>0.522230600272756</v>
+        <v>0.61921597256992</v>
       </c>
       <c r="D2" t="n">
-        <v>0.47900715344489</v>
+        <v>0.38118740130876</v>
       </c>
       <c r="E2" t="n">
-        <v>1.00123775371765</v>
+        <v>1.00040337387868</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2" t="n">
-        <v>0.478414993508098</v>
+        <v>0.381033702266369</v>
       </c>
       <c r="K2" t="n">
-        <v>0.40597366690468</v>
+        <v>0.339269321978875</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00394699443726886</v>
+        <v>0.0177987076880658</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00259314188353701</v>
+        <v>0.050851559352711</v>
       </c>
       <c r="N2" t="n">
-        <v>0.409920661341949</v>
+        <v>0.357068029666941</v>
       </c>
       <c r="O2"/>
     </row>
@@ -508,10 +508,10 @@
       <c r="D3"/>
       <c r="E3"/>
       <c r="F3" t="n">
-        <v>0.52358612856252</v>
+        <v>0.586149788248297</v>
       </c>
       <c r="G3" t="n">
-        <v>0.406476162320158</v>
+        <v>0.339406174361199</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
@@ -535,10 +535,10 @@
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4" t="n">
-        <v>0.519634248718213</v>
+        <v>0.568343901026476</v>
       </c>
       <c r="I4" t="n">
-        <v>0.365061174648288</v>
+        <v>0.370100022661873</v>
       </c>
       <c r="J4"/>
       <c r="K4"/>
@@ -546,7 +546,7 @@
       <c r="M4"/>
       <c r="N4"/>
       <c r="O4" t="n">
-        <v>0.481008135391635</v>
+        <v>0.43188526161908</v>
       </c>
     </row>
   </sheetData>
@@ -588,16 +588,16 @@
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>0.478414993508098</v>
+        <v>0.381033702266369</v>
       </c>
       <c r="D2" t="n">
-        <v>0.38869476321529</v>
+        <v>0.31681818860577</v>
       </c>
       <c r="E2" t="n">
-        <v>0.568135223800905</v>
+        <v>0.445249215926968</v>
       </c>
       <c r="F2" t="n">
-        <v>388</v>
+        <v>946</v>
       </c>
     </row>
     <row r="3">
@@ -608,16 +608,16 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.409920661341949</v>
+        <v>0.357068029666941</v>
       </c>
       <c r="D3" t="n">
-        <v>0.280807322446425</v>
+        <v>0.260390654899495</v>
       </c>
       <c r="E3" t="n">
-        <v>0.539034000237474</v>
+        <v>0.453745404434388</v>
       </c>
       <c r="F3" t="n">
-        <v>388</v>
+        <v>946</v>
       </c>
     </row>
     <row r="4">
@@ -628,16 +628,16 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.481008135391635</v>
+        <v>0.43188526161908</v>
       </c>
       <c r="D4" t="n">
-        <v>0.353210434510059</v>
+        <v>0.336037310670792</v>
       </c>
       <c r="E4" t="n">
-        <v>0.60880583627321</v>
+        <v>0.527733212567368</v>
       </c>
       <c r="F4" t="n">
-        <v>388</v>
+        <v>946</v>
       </c>
     </row>
   </sheetData>
